--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_05_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_05_21_Cau.xlsx
@@ -723,7 +723,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người kiểm tra phải biết ai làm gì, trên đầu vào nào, kết quả/trạng thái/bao lâu.</t>
+          <t>Một bản ghi dấu vết (trace record / span) hoàn chỉnh để tái dựng trạng thái và hành động của agent/node cần: (a) Trace/Run ID; (b) Dấu thời gian (timestamp); (c) Định danh duy nhất của agent/node thực hiện; (d) Tên hành động hoặc tool được gọi; (e) Tóm tắt dữ liệu vào/ra trong phạm vi được phép; (f) Trạng thái thực thi và độ trễ (latency). Tuyệt đối không lưu trữ các bí mật bảo mật hoặc prompt thô chứa dữ liệu nhạy cảm.</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một lỗi không được biến thành việc hoàn tất âm thầm.</t>
+          <t>Chính sách cô lập lỗi có kiểm soát cho worker gọi dịch vụ từ xa bao gồm: (a) Cấu hình timeout rõ ràng; (b) Thử lại có giới hạn (exponential backoff) chỉ áp dụng cho lỗi tạm thời; (c) Có phương án dự phòng bảo toàn nguồn gốc dữ liệu; (d) Cho phép trả lời một phần kèm công bố minh bạch phần dữ liệu còn thiếu. Không được thử lại vô hạn hay nuốt lỗi.</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nếu đầu vào/tiêu chí đổi thì không thể quy khác biệt cho kiến trúc.</t>
+          <t>Một nghiên cứu đối chiếu hợp lệ giữa kiến trúc Single-Agent và Multi-Agent bắt buộc phải: (a) Dùng chung một bộ câu hỏi kiểm thử và tiêu chí chấm điểm đóng băng; (b) Đánh giá đa chiều trên các khía cạnh: chất lượng, độ trễ, chi phí token, và tỷ lệ từ chối/không trả lời; (c) Cung cấp khả năng chẩn đoán dấu vết chi tiết cho từng ca kiểm thử; (d) Kiểm tra kỹ lưỡng các ca hồi quy (regressions) ở cấp từng trường hợp cụ thể.</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ chọn thứ code có thể quyết từ dữ kiện/contract đầy đủ.</t>
+          <t>Các thành phần của artifact cuối cùng có thể kiểm tra tự động bằng quy tắc xác định (deterministic rules) trước khi công bố: (a) Tính hợp lệ của cấu trúc JSON schema và các trường bắt buộc; (b) Sự tồn tại của các mã định danh tham chiếu trong cơ sở dữ liệu; (c) Tổng tỷ lệ phân bổ phần trăm đạt chính xác 100%; (d) Giá trị trạng thái thuộc danh mục enum cho phép. Diễn giải pháp lý là yếu tố chủ quan, không thể kiểm tra bằng luật xác định.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_05_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_05_21_Cau.xlsx
@@ -669,10 +669,42 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xác định thứ bên gọi thực sự cần sau khi nhóm hoàn tất.
-Phân tích theo nguyên lý thiết kế: Xác định thứ bên gọi thực sự cần sau khi nhóm hoàn tất.</t>
+- [Phê phán lỗi phá vỡ tính bao gói] (1.0 điểm): Chỉ ra việc đồ thị chính đọc biến nội bộ làm mất tính tái sử dụng của module Finance.
+- [Thiết kế Input/Output Contract cho Subgraph] (1.5 điểm): Định nghĩa schema đầu vào tối thiểu và schema đầu ra sạch sẽ (decision, amount, citations).
+- [Chỉ rõ các trường nội bộ bắt buộc phải ẩn] (1.5 điểm): Liệt kê chính xác việc ẩn raw retrieval, policy tmp, và retry count bên trong subgraph.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích lỗi rò rỉ đóng gói của thiết kế hiện tại:
+Đồ thị chính đang đọc trực tiếp các biến nội bộ cấp thấp (`finance_retrieval_raw`, `finance_policy_tmp`, `finance_retry_count`) của ba node bên trong luồng Finance. Đây là lỗi vi phạm nghiêm trọng Tính Bao gói (Encapsulation Leak / Tight Coupling): Đồ thị chính bị dính chặt vào chi tiết cài đặt của luồng Finance, khiến luồng này không thể tái sử dụng độc lập ở ứng dụng khác.
+2. Thiết kế Hợp đồng Đầu vào / Đầu ra cho Subgraph Finance (Clean Subgraph Contract):
+Đóng gói toàn bộ luồng Finance thành một LangGraph Subgraph khép kín với State Interface rõ ràng:
+- **Hợp đồng Đầu vào (Subgraph Input Contract)**:
+  ```json
+  {
+    "case_id": "string",
+    "applicant_id": "string",
+    "requested_amount": "number",
+    "claim_category": "string"
+  }
+  ```
+- **Hợp đồng Đầu ra (Subgraph Output Contract - Chỉ trả kết quả nghiệp vụ cuối cùng)**:
+  ```json
+  {
+    "case_id": "string",
+    "finance_decision": "APPROVED | REJECTED",
+    "approved_amount": "number",
+    "policy_citations": ["string"],
+    "rejection_reason": "string (optional)"
+  }
+  ```
+3. Phần BẮT BUỘC PHẢI ẨN bên trong Subgraph (Private Internal State):
+- Ẩn hoàn toàn `finance_retrieval_raw` (dữ liệu văn bản thô trích xuất từ tài liệu).
+- Ẩn hoàn toàn `finance_policy_tmp` (các biến tính toán trung gian tạm thời).
+- Ẩn hoàn toàn `finance_retry_count` (bộ đếm số lần thử lại nội bộ).
+Bên ngoài chỉ nhìn thấy Hợp đồng Đầu ra chuẩn mực, cho phép cắm Subgraph vào bất kỳ ứng dụng nào.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thiết kế Subgraph trong Kiến trúc Tác tử: 'Private by default, Public by contract'. Một Subgraph chất lượng cao phải che giấu toàn bộ các biến tạm thời và cơ chế thử lại nội bộ (Information Hiding), chỉ phơi bày các thuộc tính đầu ra mang giá trị nghiệp vụ thực sự cho đồ thị cha.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Documentation: 'Subgraphs and Multi-Graph Systems' (https://langchain-ai.github.io/langgraph/how-tos/subgraph/)</t>
         </is>
       </c>
     </row>
@@ -754,10 +786,51 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Dùng tham chiếu/tóm tắt cho payload nhạy cảm.
-Phân tích theo nguyên lý thiết kế: Dùng tham chiếu/tóm tắt cho payload nhạy cảm.</t>
+- [Đặc tả Multiagent Trace Schema phân tầng] (1.5 điểm): Thiết kế schema đầy đủ: trace_id, span_id, parent_span_id, node_name, timing, token usage.
+- [Minh họa hành trình 4 node rõ ràng] (1.5 điểm): Thể hiện chuỗi span qua retrieval -&gt; policy -&gt; tool -&gt; synthesis với input/output summary.
+- [Khử PII và che chắn thông tin nhạy cảm] (1.0 điểm): Áp dụng băm user_ref_hash và mặt nạ hóa tài khoản (ACC_***4491) bảo vệ quyền riêng tư.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đề xuất Lược đồ Trace Đa tác tử (Multiagent Trace Schema Definition):
+Thiết kế schema trace phân cấp tuân thủ chuẩn OpenTelemetry / W3C TraceContext, ghi lại hành trình qua các node:
+```json
+{
+  "trace_id": "string (UUID v4 đại diện cho toàn bộ phiên)",
+  "session_id": "string",
+  "user_ref_hash": "string (Mã băm định danh người dùng - KHÔNG LƯU PII THÔ)",
+  "spans": [
+    {
+      "span_id": "string",
+      "parent_span_id": "string (optional)",
+      "node_name": "retrieval | policy | payment_tool | synthesis",
+      "start_time": "ISO-8601",
+      "end_time": "ISO-8601",
+      "status": "SUCCESS | ERROR",
+      "input_summary": "dict (tham chiếu hoặc dữ liệu đã khử PII)",
+      "output_summary": "dict",
+      "token_usage": {"prompt_tokens": 0, "completion_tokens": 0},
+      "error_details": "string (optional)"
+    }
+  ]
+}
+```
+2. Minh họa Bản ghi Trace Mẫu không làm lộ PII (Sanitized Sample Trace Record):
+Minh họa lượt chạy qua 4 node với dữ liệu người dùng đã được che chắn an toàn:
+```json
+{
+  "trace_id": "tr-8891-b4a1-49f2",
+  "user_ref_hash": "sha256:4a5e1e...",
+  "spans": [
+    {"span_id": "sp-01", "node_name": "retrieval", "input_summary": {"query_topic": "tuition_refund"}, "output_summary": {"matched_chunk_ids": ["doc_8::chk_2"], "count": 1}},
+    {"span_id": "sp-02", "parent_span_id": "sp-01", "node_name": "policy", "input_summary": {"doc_ref": "doc_8::chk_2"}, "output_summary": {"eligible": true, "rate": 1.0}},
+    {"span_id": "sp-03", "parent_span_id": "sp-02", "node_name": "payment_tool", "input_summary": {"action": "verify_balance", "account_ref": "ACC_***4491"}, "output_summary": {"status": "verified"}},
+    {"span_id": "sp-04", "parent_span_id": "sp-03", "node_name": "synthesis", "input_summary": {"decision": "approved"}, "output_summary": {"final_answer_length": 240, "citations": ["doc_8"]}}
+  ]
+}
+```
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khả năng quan sát (Observability) trong hệ thống tác tử đòi hỏi việc theo dõi từng span chuyển trạng thái (State Transition Span). Tuy nhiên, log trace là nơi thường xuyên bị rò rỉ dữ liệu nhạy cảm nhất. Việc băm định danh người dùng (Salted Hash) và chỉ lưu trữ bản tóm tắt hoặc tham chiếu dữ liệu (Redacted Summary) là bắt buộc theo quy định an toàn dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Specification: 'Trace and Span Data Model' &amp; OWASP LLM06 Sensitive Information Disclosure</t>
         </is>
       </c>
     </row>
@@ -837,10 +910,32 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Vẽ cây theo cạnh lời gọi, không xếp hoàn toàn theo thời gian đồng hồ thực.
-Phân tích theo nguyên lý thiết kế: Vẽ cây theo cạnh lời gọi, không xếp hoàn toàn theo thời gian đồng hồ thực.</t>
+- [Thiết kế truyền W3C Traceparent Header] (1.5 điểm): Đặc tả việc truyền trace_id toàn cục và parent_span_id xuyên suốt Supervisor, Workers và MCP.
+- [Cảnh báo lỗi dùng đồng hồ thực khi có Clock Skew] (1.0 điểm): Nhận diện đồng hồ lệch 2 giây làm sai lệch sắp xếp thời gian tuyệt đối.
+- [Dựng cây nhân quả Causal Graph chính xác] (1.5 điểm): Vẽ và giải thích cây quan hệ cha-con (span_id -&gt; parent_span_id) thể hiện đúng nhánh retry của A song song với B.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Cách truyền Thông tin Ngữ cảnh Phân tán (Distributed Context Propagation):
+Áp dụng chuẩn quốc tế **W3C Trace Context Specification** qua HTTP Headers và MCP Metadata:
+- **Header 1: `traceparent`** (Định dạng: `version-trace_id-parent_span_id-trace_flags`):
+  + `trace_id`: Một ID toàn cục duy nhất (128-bit hex) do Supervisor sinh ra khi bắt đầu phiên, được truyền nguyên vẹn xuyên suốt qua Worker A, Worker B và MCP Server.
+  + `parent_span_id`: Khi Worker A gọi MCP, nó gán `span_id` của chính nó vào vị trí parent để MCP biết nó là con của ai.
+- **Header 2: `tracestate` / Correlation ID**: Truyền tải thêm `retry_attempt = 1` khi Worker A thực hiện thử lại.
+2. Dựng Cấu trúc Nhân quả Không phụ thuộc vào Đồng hồ thực (Causal Tree Reconstruction):
+- **Vấn đề đồng hồ lệch 2 giây (Clock Skew)**: Trong hệ thống phân tán, đồng hồ giữa các server luôn có độ lệch (Skew). Tuyệt đối **KHÔNG ĐƯỢC** dùng mốc thời gian tuyệt đối (`timestamp`) để sắp xếp thứ tự thực thi của các tác vụ song song!
+- **Thuật toán dựng Cây Nhân quả (Causal Graph Reconstruction)**:
+  Hệ thống dựng cây theo đồ thị cạnh lời gọi nhân quả dựa trên cặp quan hệ `(parent_span_id -&gt; span_id)`:
+  ```text
+  [Root: Supervisor (span_0)]
+       ├── [Child 1: Worker A (span_A1)]
+       │         ├── [Child 1.1: MCP Call 1 - FAILED (span_M1)]
+       │         └── [Child 1.2: MCP Call 2 - RETRY SUCCESS (span_M2)]
+       └── [Child 2: Worker B (span_B1)]
+  ```
+- Kết quả: Cấu trúc nhân quả thể hiện chính xác Worker A gọi MCP lần 1 lỗi rồi thử lại lần 2, song song với Worker B, bất chấp đồng hồ của MCP Server có lệch trước hay sau 2 giây.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong hệ thống phân tán có độ lệch đồng hồ (Clock Skew), trật tự nhân quả (Causal Ordering) của Lamport chỉ có thể được bảo toàn thông qua mối quan hệ Phụ thuộc Cha-Con (Parent-Child Span Links) của W3C Trace Context, thay vì dựa vào nhãn thời gian vật lý.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+W3C Recommendation: 'Trace Context Specification' (https://www.w3.org/TR/trace-context/) &amp; Lamport (1978): 'Time, Clocks, and the Ordering of Events'</t>
         </is>
       </c>
     </row>
@@ -916,10 +1011,24 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So từng sự kiện với routing contract được nêu ngay trong câu.
-Phân tích theo nguyên lý thiết kế: So từng sự kiện với routing contract được nêu ngay trong câu.</t>
+- [Xác định đúng lỗi sớm nhất ở Router] (1.5 điểm): Đối chiếu với hợp đồng định tuyến, khẳng định Router điều phối nhầm sang RetrievalWorker là lỗi gốc rễ.
+- [Giải thích chuỗi lỗi dây chuyền] (1.0 điểm): Phân tích rõ Retrieval và Synthesis chỉ là nạn nhân của đầu vào sai từ Router.
+- [Đề xuất đúng 1 kiểm tra đơn vị có mục tiêu] (1.5 điểm): Viết test assertion kiểm tra Router phân loại đúng câu hỏi số dư sang BillingToolWorker.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xác định Lỗi Sớm nhất trong Chuỗi Thực thi (Earliest Defect Localization):
+- **Lỗi sớm nhất nằm ở NODE ROUTER (Routing Layer Defect)**.
+- Căn cứ đối chiếu Hợp đồng Định tuyến (Routing Contract): Hợp đồng quy định rõ ràng rằng: 'Mọi truy vấn về số dư billing hiện tại bắt buộc phải đi `BillingToolWorker`'.
+- Tuy nhiên, Router đã gửi truy vấn `Số dư hiện tại của tài khoản A?` sang `RetrievalWorker`.
+- Phân tích chuỗi domino dây chuyền: RetrievalWorker trả về các đoạn chính sách đúng schema nhưng không liên quan vì nó chỉ tra tài liệu tĩnh chứ không có dữ liệu số dư; SynthesisWorker bám theo các đoạn trích đó nên buộc phải trả lời sai. Lỗi của Retrieval và Synthesis chỉ là nạn nhân của quyết định định tuyến sai lầm sớm nhất từ Router.
+2. Đề xuất ĐÚNG MỘ KIỂM TRA TIẾP THEO CÓ MỤC TIÊU (Targeted Regression Test):
+- **Bài kiểm tra duy nhất: Kiểm thử Đơn vị cho Routing Contract (Router Intent Classification Unit Test)**:
+  + Thiết lập kiểm thử độc lập cho hàm `route(query)` với trường hợp kiểm thử:
+    `assert router.classify('Số dư hiện tại của tài khoản A?') == 'BillingToolWorker'`.
+  + Kiểm tra xem prompt của Router hoặc bộ phân loại Embedder có phân biệt được giữa 'Chính sách tính phí (Policy)' và 'Số dư tài khoản thời gian thực (Live Balance Tool)' hay không.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kỹ thuật Phân lập Lỗi Sớm nhất (Root-Cause Localization): Trong hệ thống đa tác tử nối tiếp, lỗi ở bước đầu tiên sẽ tạo ra hiệu ứng dây chuyền khiến toàn bộ các tác tử phía sau hành xử sai lệch dù mã nguồn của chúng hoàn toàn đúng. Cần tập trung sửa lỗi ở mắt xích gãy sớm nhất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE: 'Root Cause Analysis in Distributed Systems' &amp; LangGraph Testing and Evaluation</t>
         </is>
       </c>
     </row>
@@ -1046,10 +1155,25 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xử lý từng loại lỗi khác nhau, rồi quyết toàn bộ lần chạy có đủ điều kiện công bố không.
-Phân tích theo nguyên lý thiết kế: Xử lý từng loại lỗi khác nhau, rồi quyết toàn bộ lần chạy có đủ điều kiện công bố không.</t>
+- [Phê phán hành vi giấu lỗi âm thầm] (1.0 điểm): Chỉ ra việc gán completed khi B timeout và C sai schema là che giấu lỗi và lừa dối người dùng.
+- [Xử lý riêng biệt cho lỗi Timeout B và Schema C] (1.5 điểm): Thiết lập retry cho B và feedback schema cho C kèm phương án dự phòng.
+- [Chính sách kết quả một phần &amp; Trạng thái kết thúc] (1.5 điểm): Thiết lập trạng thái minh bạch (COMPLETED_WITH_WARNINGS hoặc FAILED) tùy thuộc vào tính thiết yếu của B và C.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phê phán hành vi hiện tại: Hệ thống gộp kết quả của A rồi âm thầm gán `status = 'completed'` mà hoàn toàn giấu nhẹm việc B bị timeout và C bị sai schema là một lỗi che giấu lỗi nguy hiểm (Silent Failure Masking), tạo ra kết quả thiếu hụt thông tin mà người dùng không hề hay biết.
+2. Thiết kế Chính sách Phục hồi Toàn diện (Failure Containment Policy):
+- **Chính sách Thử lại và Dự phòng cho từng loại lỗi (Error-Specific Policies)**:
+  + **Với Worker B (Hết thời gian chờ / Timeout)**: Kích hoạt Thử lại Có Giới hạn (Bounded Retry): Thử lại tối đa 1 lần (`max_retries = 1`) với exponential backoff. Nếu vẫn timeout, kích hoạt Fallback: Trả về trạng thái `PARTIAL_TIMEOUT` kèm dữ liệu cache gần nhất (nếu có).
+  + **Với Worker C (Schema không hợp lệ / Malformed Output)**: Không thử lại ngay với cùng payload. Gửi thông báo lỗi schema cụ thể cho Worker C yêu cầu sửa định dạng (`Retry with Schema Feedback`). Nếu vẫn lỗi, đánh dấu `FAILED_SCHEMA`.
+- **Quy tắc Kết quả Một phần (Partial Result Contract)**:
+  Nếu tác vụ cho phép công bố một phần, payload trả về phải công khai minh bạch trạng thái của từng worker:
+  `{"data": {"worker_A": result_A}, "warnings": ["Worker B timed out", "Worker C schema invalid"]}`.
+- **Trạng thái Kết thúc Tổng thể (Final Status Resolution)**:
+  + Nếu B và C là tác vụ bắt buộc (Critical Invariants): Toàn bộ lần chạy phải kết thúc với trạng thái **`FAILED_DEPENDENCY`** (Không được công bố).
+  + Nếu B và C là tùy chọn (Optional): Kết thúc với trạng thái **`COMPLETED_WITH_WARNINGS`** hoặc `DEGRADED_PARTIAL_SUCCESS`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khả năng Chống đỡ và Ngăn chặn Lỗi (Failure Containment): Trong xử lý phân tán song song, không bao giờ được phép đồng nhất thành công một phần với thành công toàn diện. Mỗi loại lỗi (Timeout vs Schema Error) đòi hỏi chiến lược khắc phục riêng, và trạng thái kết thúc phải phản ánh trung thực mức độ toàn vẹn của kết quả.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: 'Addressing Cascading Failures &amp; Graceful Degradation' &amp; Resilience4j Circuit Breaker Patterns</t>
         </is>
       </c>
     </row>
@@ -1131,10 +1255,24 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân nhóm theo nơi lợi ích xuất hiện.
-Phân tích theo nguyên lý thiết kế: Phân nhóm theo nơi lợi ích xuất hiện.</t>
+- [Kết luận có điều kiện dựa trên phân nhóm rủi ro] (1.5 điểm): Khẳng định Multi-Agent chỉ xứng đáng ở nhóm rủi ro cao (giảm 20% lỗi không bằng chứng), không đáng ở nhóm rủi ro thấp.
+- [Phân tích đánh đổi định lượng cụ thể] (1.0 điểm): Nêu rõ trade-off: chất lượng +4% đổi lấy độ trễ gấp 3 (9s) và chi phí gấp 3 (3x token).
+- [Đề xuất triển khai định tuyến thích ứng theo rủi ro] (1.5 điểm): Đưa ra kiến trúc định tuyến thông minh: Low-risk đi Single-Agent, High-risk đi Multi-Agent.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Kết luận có điều kiện dựa trên dữ liệu thực nghiệm (Conditional Conclusion):
+- Đánh đổi quan sát được: Multi-Agent nâng chất lượng từ 0.82 lên 0.86 (+4%), nhưng phải trả giá bằng việc độ trễ p95 tăng gấp 3 lần (từ 3s lên 9s) và chi phí token tăng gấp 3 lần (`cost = 3x`).
+- **Kết luận điều kiện**: **MULTI-AGENT CHỈ ĐÁNG GIÁ TRÊN CÁC TRƯỜNG HỢP RỦI RO CAO (HIGH-STAKE DOMAINS)**. Trên các trường hợp rủi ro cao, Multi-Agent giảm được 20% các tuyên bố không có bằng chứng (giảm hallucination/thiệt hại pháp lý), hoàn toàn bù đắp được chi phí 3x và độ trễ 9s. Ngược lại, trên các trường hợp rủi ro thấp, chất lượng hai bên ngang nhau nên việc dùng Multi-Agent là hoàn toàn lãng phí.
+2. Đề xuất Kiến trúc Triển khai Định tuyến Thích ứng (Adaptive Routing Deployment):
+Triển khai kiến trúc Định tuyến theo Rủi ro (Risk-Tiered Routing Architecture):
+- **Tầng Rủi ro Thấp (Low-risk queries - Câu hỏi thông thường, FAQ, tra cứu thông tin cơ bản)**:
+  + Định tuyến sang **Single-Agent Pipeline**: Giữ độ trễ cực nhanh p95 = 3s và chi phí 1x.
+- **Tầng Rủi ro Cao (High-risk queries - Quyết định hoàn tiền, chính sách pháp lý, tranh chấp)**:
+  + Định tuyến sang **Multi-Agent Pipeline** (có Verifier và Reflection): Chấp nhận p95 = 9s để tận dụng mức giảm 20% ảo giác và bảo đảm tính chính xác tuyệt đối.
+3. Kế hoạch Đánh giá Tiếp theo: Theo dõi chi phí thực tế và tỷ lệ hài lòng của người dùng trên từng phân khúc rủi ro.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kiến trúc sư AI không được thiên vị công nghệ (No Silver Bullet): Multi-Agent mang lại khả năng tự phản biện và giảm ảo giác trên các bài toán phức tạp, nhưng lại mang gánh nặng độ trễ và chi phí khổng lồ. Mô hình Hybrid Routing phân chia theo mức độ rủi ro (Risk-Based Tiering) là giải pháp kinh tế kỹ thuật tối ưu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic AI Research: 'Evaluating Multi-Agent vs. Single-Agent Tradeoffs' &amp; Google Cloud Architecture Cost Optimization</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1303,32 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Vẽ supervisor → {A,B} → bước gộp kết quả.
-Phân tích theo nguyên lý thiết kế: Vẽ supervisor → {A,B} → bước gộp kết quả.</t>
+- [Tính đúng độ trễ đường găng 1.100 ms] (1.5 điểm): Thể hiện rõ phép tính 100 + max(500, 800) + 200 = 1.100 ms.
+- [Tính đúng tổng số 4 lời gọi] (1.0 điểm): Liệt kê đủ 1 Supervisor + 1 A + 1 B + 1 Gộp = 4 lời gọi model/tool.
+- [Giải thích bản chất song song max(A, B)] (1.5 điểm): Giải thích rõ ràng vì sao không cộng A+B do chạy đồng thời, thời gian bị chặn bởi nhánh B chạy chậm nhất.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Độ trễ Đường găng (Critical Path Latency Computation):
+- Phân tích luồng thực thi: `Supervisor` -&gt; `{Worker A // Worker B chạy song song}` -&gt; `Gộp kết quả`.
+- Thời gian thực thi của từng node:
+  + Supervisor (chạy trước): `100 ms`.
+  + Hai worker A và B chạy song song (Parallel Concurrent Execution):
+    Worker A mất `500 ms`, Worker B mất `800 ms`. Do chạy song song trên hai luồng độc lập, thời gian chờ của giai đoạn này được quyết định bởi nhánh chạy chậm nhất (Straggler / Bottleneck Node):
+    `T_parallel = max(Latency_A, Latency_B) = max(500 ms, 800 ms) = 800 ms`.
+  + Bước gộp kết quả (chạy sau khi cả hai worker hoàn thành): `200 ms`.
+- **Tổng độ trễ đường găng (Critical Path Latency)**:
+  `Latency_Critical_Path = 100 ms + 800 ms + 200 ms = 1.100 ms` (tức 1,1 giây).
+2. Tính toán Số lời gọi Model/Tool:
+- Supervisor: 1 lời gọi.
+- Worker A: 1 lời gọi.
+- Worker B: 1 lời gọi.
+- Bước gộp kết quả: 1 lời gọi.
+- **Tổng số lời gọi thực hiện**: `1 + 1 + 1 + 1 = 4 lời gọi`.
+3. Giải thích vì sao KHÔNG ĐƯỢC CỘNG A + B:
+Vì Worker A và Worker B được kích hoạt đồng thời (Asynchronous Parallelism). Khi Worker B đang chạy ở mili-giây thứ 500, Worker A đã hoàn thành công việc của mình và chuyển sang trạng thái chờ tại rào cản đồng bộ (Barrier). Hai tác vụ tiêu tốn thời gian đồng thời trên dòng thời gian thực, do đó độ trễ là hàm `max(A, B)` chứ không phải hàm tổng `A + B` (phép cộng `500 + 800 = 1300 ms` chỉ xảy ra khi chạy tuần tự).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khái niệm Đường găng (Critical Path Method - CPM) trong kiến trúc đồ thị phân tán: Độ trễ toàn trình của một cấu trúc phân nhánh song song (Fan-out / Fan-in) được xác định bằng mắt xích có thời gian thực thi dài nhất trong tập các tác vụ đồng thời.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Cormen et al.: 'Introduction to Algorithms' - Chapter on Multithreaded Algorithms &amp; Google SRE Latency Analysis</t>
         </is>
       </c>
     </row>
@@ -1199,10 +1359,35 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tính token cơ sở của mỗi node trước; không có giá nhà cung cấp nên không thể tính tiền.
-Phân tích theo nguyên lý thiết kế: Tính token cơ sở của mỗi node trước; không có giá nhà cung cấp nên không thể tính tiền.</t>
+- [Tính đúng Worst-case Token = 17.400 tokens] (1.5 điểm): Thể hiện phép tính: 1200 + 1200 + (3 * 2 * 2500) = 17.400 tokens (14.000 in, 3.400 out).
+- [Tính đúng độ trễ đường găng 2,5 giây] (1.0 điểm): Tính đúng 0,2s + 2,0s + 0,3s = 2,5s khi không có retry.
+- [Thiết kế phương án dự phòng Circuit Breaker] (1.5 điểm): Đưa ra chính sách ngắt mạch khi chạm trần budget: hủy retry, trả partial result hoặc fallback an toàn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Token trong trường hợp xấu nhất (Worst-Case Token Consumption):
+- Token cơ sở của từng node:
+  + Supervisor: 1.000 input + 200 output = `1.200 tokens`.
+  + Bước gộp kết quả: 1.000 input + 200 output = `1.200 tokens`.
+  + Mỗi worker (1 lần gọi): 2.000 input + 500 output = `2.500 tokens`.
+- Trường hợp xấu nhất của 3 worker song song:
+  Cả 3 worker đều thất bại ở lần gọi đầu và phải thử lại tối đa 1 lần (tổng cộng mỗi worker gọi 2 lần = 6 lượt gọi worker).
+  Token của 3 worker trong worst-case: `3 workers * 2 lần gọi * 2.500 tokens = 15.000 tokens` (trong đó input = `12.000`, output = `3.000`).
+- **Tổng token trường hợp xấu nhất**:
+  `Tổng Token = 1.200 (Supervisor) + 1.200 (Gộp) + 15.000 (3 Workers x 2) = 17.400 tokens`
+  (Bao gồm: `14.000 tokens đầu vào` và `3.400 tokens đầu ra`).
+2. Tính toán Độ trễ Đường găng KHÔNG thử lại (Critical Path Latency without retries):
+- Supervisor: `0,2s`.
+- 3 Workers song song không thử lại: `max(2s, 2s, 2s) = 2,0s`.
+- Bước gộp kết quả: `0,3s`.
+- **Tổng độ trễ đường găng**: `0,2s + 2,0s + 0,3s = 2,5 giây`.
+3. Phương án dự phòng khi Vượt Ngân sách (Budget Exceeded Fallback Policy):
+- **Ngắt mạch Tự động (Circuit Breaker / Budget Cap Guardrail)**: Thiết lập ngưỡng chặn cứng (Hard Cap) về token (ví dụ: 14.000 tokens) hoặc độ trễ (3,5s). Khi tích lũy chạm ngưỡng:
+  + Ngay lập tức hủy (cancel) các yêu cầu thử lại đang chạy dở dang của các worker.
+  + Sử dụng Kết quả Một phần (Degraded Partial Result) từ các worker đã kịp hoàn thành trước đó.
+  + Nếu không đủ dữ liệu cốt lõi, fallback về câu trả lời an toàn mặc định thông báo quá tải hệ thống, ngăn chặn việc chi phí token bùng nổ vô hạn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quản lý Ngân sách và Độ trễ (Cost &amp; Latency Budgeting) trong hệ thống tác tử: Luôn phải tính toán kịch bản cận trên xấu nhất (Worst-Case Upper Bound) có tính đến số lần thử lại tối đa. Cơ chế Circuit Breaker là phanh hãm kỹ thuật bắt buộc để bảo vệ doanh nghiệp khỏi các hóa đơn token khổng lồ bất ngờ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE: 'Managing Cascading Retries and Token Budgets' &amp; Resilience4j Architecture</t>
         </is>
       </c>
     </row>
@@ -1327,10 +1512,33 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một citation có thể đúng file nhưng vẫn không hỗ trợ đúng mệnh đề.
-Phân tích theo nguyên lý thiết kế: Một citation có thể đúng file nhưng vẫn không hỗ trợ đúng mệnh đề.</t>
+- [Chẩn đoán lỗi làm rơi nguồn tại PolicyWorker] (1.0 điểm): Chỉ ra PolicyWorker bỏ rơi source khiến Synthesis trích dẫn chung chung vô căn cứ.
+- [Thiết kế Evidence Envelope bàn giao nguồn] (1.5 điểm): Định nghĩa cấu trúc bàn giao chuẩn mang đầy đủ claim, value và evidence_citations (chunk_id, page, quote).
+- [Bản đồ mệnh đề &amp; Handoff Assertion Gate] (1.5 điểm): Thiết lập bản đồ claim-to-source và assertion chặn luồng nếu worker trung gian làm rơi mất citation.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích hiện tượng Mất dấu Nguồn gốc (Provenance Loss Defect):
+- RetrievalWorker trích xuất 2 chunk có định danh nguồn rõ ràng: `[C1: policy.pdf#page=4]`, `[C2: policy.pdf#page=12]`.
+- PolicyWorker xử lý điều kiện, trả về `eligible=true` nhưng **làm rơi mất trường trích dẫn nguồn** (Dropped Provenance).
+- SynthesisWorker ở cuối chuỗi nhận `eligible=true` mà không biết xuất phát từ chunk nào, nên đành 'đoán mò' và trích dẫn chung chung `policy.pdf`. Hậu quả: Người dùng không thể xác minh được khẳng định `eligible=true` được bảo chứng bởi điều khoản cụ thể nào.
+2. Thiết kế Cơ chế Bàn giao có Bảo toàn Nguồn gốc (Provenance-Preserving Handoff):
+Mọi bước chuyển giao trạng thái giữa các worker bắt buộc phải sử dụng **Đối tượng Bằng chứng Được Đóng gói (Evidence Envelope Pattern)**:
+```json
+{
+  "fact_id": "ELIGIBILITY_DECISION_01",
+  "claim_statement": "Học viên đủ điều kiện hoàn 100% học phí",
+  "value": true,
+  "evidence_citations": [
+    {"doc_id": "policy.pdf", "chunk_id": "C1", "page": 4, "exact_quote": "Hoàn 100% nếu rút hồ sơ trước ngày khai giảng 7 ngày"}
+  ]
+}
+```
+3. Bản đồ Mệnh đề và Kiểm tra Hợp đồng (Claim-to-Source Mapping Verification):
+- **Bản đồ Mệnh đề (Claim-to-Source Map)**: SynthesisWorker ánh xạ từng câu khẳng định trong phản hồi với mảng `evidence_citations` tương ứng.
+- **Bộ kiểm tra Handoff Guardrail**: Thiết lập assertion giữa các node: `assert len(policy_output.evidence_citations) &gt; 0` — Nếu PolicyWorker trả về phán quyết mà không đính kèm source IDs từ RetrievalWorker, hệ thống chặn lại và báo lỗi hợp đồng bàn giao ngay lập tức.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong quy trình đa tác tử, sự thất thoát dấu vết nguồn gốc (Provenance Loss) thường xảy ra ở các tác tử trung gian khi chúng chỉ truyền kết quả logic mà quên chuyển tiếp bằng chứng nền tảng. Khái niệm 'Evidence Envelope' bảo đảm mọi khẳng định luôn mang theo hộ chiếu nguồn gốc cho tới tận câu trả lời cuối cùng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+W3C PROV-DM: The PROV Data Model for Provenance &amp; LangSmith Trace Provenance Guidelines</t>
         </is>
       </c>
     </row>
@@ -1412,10 +1620,30 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách việc phát hiện từng invariant khỏi quyết định công bố.
-Phân tích theo nguyên lý thiết kế: Tách việc phát hiện từng invariant khỏi quyết định công bố.</t>
+- [Phát hiện đầy đủ 3 vi phạm bất biến] (1.5 điểm): Vạch trần chính xác: status 'done' sai enum, allocations thiếu mục và tổng=90!=100, và source S9 không tồn tại.
+- [Đặc tả báo cáo Verifier có cấu trúc] (1.0 điểm): Thiết kế kết quả của verifier xuất ra danh sách các lỗi vi phạm cụ thể.
+- [Hành vi công bố: Chặn tuyệt đối &amp; Retry/Escalate] (1.5 điểm): Quyết định chặn công bố, kích hoạt retry có feedback, và chuyển cấp con người nếu không sửa được.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Kết quả của Bộ Kiểm tra (Verifier Gate Output):
+Bộ kiểm tra (Verifier) thực hiện kiểm tra độc lập từng điều kiện bất biến (Invariant Checks) và xuất ra báo cáo lỗi có cấu trúc chi tiết:
+- **Phát hiện Vi phạm 1 (Status Invariant Violation)**:
+  Artifact trả về `status = 'done'`. Bất biến yêu cầu: `status in ['approved', 'rejected']`. Kết quả: **VI PHẠM (Invalid Status Enum)**.
+- **Phát hiện Vi phạm 2 (Allocations Count &amp; Sum Violation)**:
+  Artifact có 2 mục phân bổ với tổng bằng 90 (`len(allocations) == 2`, `sum = 90`). Bất biến yêu cầu: `len(allocations) == 3` và `sum(allocations) == 100`. Kết quả: **VI PHẠM (Missing Allocation Item &amp; Sum Incomplete)**.
+- **Phát hiện Vi phạm 3 (Source Existence Violation)**:
+  Artifact chứa source `S9`. Bất biến yêu cầu: Mọi source ID phải tồn tại trong cơ sở dữ liệu nguồn đã duyệt. Kiểm tra thấy `S9` không tồn tại. Kết quả: **VI PHẠM (Phantom / Invalid Source ID)**.
+- **Báo cáo tổng hợp của Verifier**:
+  `{"is_valid": false, "violations_count": 3, "violations": ["INVALID_STATUS_DONE", "ALLOCATION_COUNT_AND_SUM_MISMATCH", "NONEXISTENT_SOURCE_S9"]}`.
+2. Thiết kế Hành vi Công bố (Publication Behavior):
+- **Quyết định: CHẶN TUYỆT ĐỐI VIỆC CÔNG BỐ (ABORT / BLOCK PUBLICATION)**.
+- Hành vi hệ thống:
+  + Chuyển trạng thái Artifact sang `REJECTED_BY_VERIFIER` và lưu vào bảng theo dõi lỗi kiểm toán.
+  + Kích hoạt vòng phản hồi sửa lỗi (Self-Correction Loop) gửi lại báo cáo 3 vi phạm cho Agent tạo sinh để sửa đổi (tối đa 1 lần thử lại).
+  + Nếu sau thử lại vẫn không vượt qua Verifier Gate, lập tức chuyển cấp lên Quản trị viên con người, tuyệt đối không xuất bản dữ liệu lỗi ra bên ngoài.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Cổng Kiểm định Đầu ra (Output Verification Gate) là chốt chặn an toàn cuối cùng trước khi một artifact do AI tạo ra được công bố ra thế giới bên ngoài. Tách bạch việc 'phát hiện từng bất biến bị vi phạm' khỏi 'quyết định công bố' bảo đảm tính minh bạch, hỗ trợ khả năng tự sửa lỗi và ngăn chặn triệt để dữ liệu sai lệch gây hậu quả nghiệp vụ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic Model Context Protocol: 'Verification Gates' &amp; Martin Fowler: 'Specification Pattern and Invariant Validation'</t>
         </is>
       </c>
     </row>
